--- a/wijha-offers-template.xlsx
+++ b/wijha-offers-template.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>الطيران مشمول؟</t>
+          <t>الطيران شامل؟</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>كل سؤال وجوابه في سطر:  هل التأشيرة مشمولة؟ لا، على حسابك</t>
+          <t>كل سؤال وجوابه في سطر:  هل التأشيرة شاملة؟ لا، على حسابك</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       <c r="AC4" s="5" t="inlineStr"/>
       <c r="AD4" s="5" t="inlineStr">
         <is>
-          <t>هل التأشيرة مشمولة؟ نعم، التأشيرة مشمولة.</t>
+          <t>هل التأشيرة شاملة؟ نعم، التأشيرة شاملة.</t>
         </is>
       </c>
     </row>
